--- a/skills/dataiku-diagnosis-checklist-review/resources/checklist_template.xlsx
+++ b/skills/dataiku-diagnosis-checklist-review/resources/checklist_template.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enterprise-grade Security, Perm" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generative AI Acceleration &amp; In" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalable Performance, Stability" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Advanced Security Options (DSS " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Advanced Security Options (DSS)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
